--- a/xn.xlsx
+++ b/xn.xlsx
@@ -133,73 +133,541 @@
           <t>2026-04-03T08:35:37.723739+00:00</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>23484</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Terrain rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-05T06:18:10.701129+00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3065</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>23484</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Terrain rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-05T06:18:16.199259+00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3065</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>23484</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Terrain rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-05T06:18:25.157020+00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>23484</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Terrain rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-05T06:18:32.815405+00:00</t>
+        </is>
+      </c>
+      <c r="B6">
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="C6">
         <v>-1</v>
       </c>
-      <c r="D2">
+      <c r="D6">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>paused</t>
         </is>
       </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>5.5</v>
-      </c>
-      <c r="K2">
-        <v>13.5</v>
-      </c>
-      <c r="L2">
+      <c r="I6">
+        <v>7.6</v>
+      </c>
+      <c r="J6">
+        <v>5.2</v>
+      </c>
+      <c r="K6">
+        <v>12.9</v>
+      </c>
+      <c r="L6">
         <v>0</v>
       </c>
-      <c r="M2">
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>2937</v>
+      </c>
+      <c r="O6">
+        <v>42</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <v>500</v>
+      </c>
+      <c r="R6">
+        <v>2356</v>
+      </c>
+      <c r="S6">
         <v>31</v>
       </c>
-      <c r="N2">
-        <v>3209</v>
-      </c>
-      <c r="O2">
-        <v>36</v>
-      </c>
-      <c r="P2">
-        <v>5</v>
-      </c>
-      <c r="Q2">
-        <v>656</v>
-      </c>
-      <c r="R2">
-        <v>2476</v>
-      </c>
-      <c r="S2">
-        <v>31</v>
-      </c>
-      <c r="T2">
+      <c r="T6">
         <v>60</v>
       </c>
-      <c r="U2">
+      <c r="U6">
         <v>1</v>
       </c>
-      <c r="V2">
+      <c r="V6">
         <v>23484</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Terrain rebuild</t>
         </is>

--- a/xn.xlsx
+++ b/xn.xlsx
@@ -130,7 +130,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03T08:35:37.723739+00:00</t>
+          <t>2026-04-08T11:50:09.460764+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -170,62 +170,62 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>581</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -235,7 +235,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>2724844</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -247,7 +247,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-05T06:18:10.701129+00:00</t>
+          <t>2026-04-08T11:50:25.364232+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -287,37 +287,37 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -327,22 +327,22 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>535</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -352,7 +352,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>2724844</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -364,7 +364,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-05T06:18:16.199259+00:00</t>
+          <t>2026-04-08T11:50:40.838703+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -404,37 +404,37 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -444,22 +444,22 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>546</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>2724844</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-05T06:18:25.157020+00:00</t>
+          <t>2026-04-08T11:50:56.462014+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,62 +521,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>531</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>2724844</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -598,78 +598,198 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-05T06:18:32.815405+00:00</t>
-        </is>
-      </c>
-      <c r="B6">
+          <t>2026-04-08T11:51:12.730249+00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4537</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4537</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2294</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>11702</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>6832</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2724844</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Terrain rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-08T12:27:51.344644+00:00</t>
+        </is>
+      </c>
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>-1</v>
-      </c>
-      <c r="D6">
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="D7">
+        <v>313</v>
+      </c>
+      <c r="E7">
+        <v>64161</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>warm</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>paused</t>
         </is>
       </c>
-      <c r="I6">
-        <v>7.6</v>
-      </c>
-      <c r="J6">
-        <v>5.2</v>
-      </c>
-      <c r="K6">
-        <v>12.9</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>23</v>
-      </c>
-      <c r="N6">
-        <v>2937</v>
-      </c>
-      <c r="O6">
-        <v>42</v>
-      </c>
-      <c r="P6">
-        <v>5</v>
-      </c>
-      <c r="Q6">
-        <v>500</v>
-      </c>
-      <c r="R6">
-        <v>2356</v>
-      </c>
-      <c r="S6">
-        <v>31</v>
-      </c>
-      <c r="T6">
-        <v>60</v>
-      </c>
-      <c r="U6">
+      <c r="I7">
+        <v>409.5</v>
+      </c>
+      <c r="J7">
+        <v>100.5</v>
+      </c>
+      <c r="K7">
+        <v>510</v>
+      </c>
+      <c r="L7">
+        <v>155</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+      <c r="N7">
+        <v>3379</v>
+      </c>
+      <c r="O7">
+        <v>35</v>
+      </c>
+      <c r="P7">
+        <v>4</v>
+      </c>
+      <c r="Q7">
+        <v>577</v>
+      </c>
+      <c r="R7">
+        <v>2723</v>
+      </c>
+      <c r="S7">
+        <v>34</v>
+      </c>
+      <c r="T7">
+        <v>153.7</v>
+      </c>
+      <c r="U7">
         <v>1</v>
       </c>
-      <c r="V6">
+      <c r="V7">
         <v>23484</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Terrain rebuild</t>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>HDF render</t>
         </is>
       </c>
     </row>
